--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SOCAGE JOVENS L’ELIANA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SOCAGE JOVENS L’ELIANA.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1669</v>
+        <v>2.1608</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9427</v>
+        <v>1.1019</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2241</v>
+        <v>1.0589</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5624</v>
+        <v>1.5553</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7398</v>
+        <v>-0.7595</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3022</v>
+        <v>2.3148</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5853</v>
+        <v>1.6881</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2963</v>
+        <v>-0.2411</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8816</v>
+        <v>1.9292</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.023</v>
+        <v>-0.1328</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4435</v>
+        <v>-0.5184</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4205</v>
+        <v>0.3856</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1237</v>
+        <v>-1.1034</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7023</v>
+        <v>-0.671</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4214</v>
+        <v>-0.4324</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3278</v>
+        <v>0.3457</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X2" t="n">
-        <v>0.068</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6934</v>
+        <v>1.6663</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2622</v>
+        <v>0.4832</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4312</v>
+        <v>1.1831</v>
       </c>
       <c r="G3" t="n">
-        <v>5.0847</v>
+        <v>5.0899</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1445</v>
+        <v>2.1511</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9402</v>
+        <v>2.9387</v>
       </c>
       <c r="J3" t="n">
-        <v>3.423</v>
+        <v>3.5436</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5814</v>
+        <v>1.655</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8416</v>
+        <v>1.8887</v>
       </c>
       <c r="M3" t="n">
-        <v>1.6617</v>
+        <v>1.5462</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5631</v>
+        <v>0.4961</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0985</v>
+        <v>1.0501</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8597</v>
+        <v>-0.8529</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-0.9183</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1005</v>
+        <v>0.0654</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.3315</v>
+        <v>-2.3759</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.3315</v>
+        <v>-2.3759</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7426</v>
+        <v>0.6172</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8108</v>
+        <v>0.8686</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0682</v>
+        <v>-0.2513</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6172</v>
+        <v>-1.6689</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5977</v>
+        <v>-1.6087</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0194</v>
+        <v>-0.0602</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5161</v>
+        <v>-0.4769</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.276</v>
+        <v>-1.2469</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7599</v>
+        <v>0.77</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.101</v>
+        <v>-1.192</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3217</v>
+        <v>-0.3618</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7793</v>
+        <v>-0.8302</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2791</v>
+        <v>1.2609</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0671</v>
+        <v>1.066</v>
       </c>
       <c r="U4" t="n">
-        <v>0.212</v>
+        <v>0.1949</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0803</v>
+        <v>0.0516</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1795</v>
+        <v>-0.2279</v>
       </c>
     </row>
     <row r="5">
@@ -799,31 +799,31 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.176</v>
+        <v>-1.1947</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.2455</v>
+        <v>-2.1429</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0696</v>
+        <v>0.9482</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2306</v>
+        <v>-0.2718</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0425</v>
+        <v>0.0184</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2731</v>
+        <v>-0.2902</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5362</v>
+        <v>-0.489</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0218</v>
+        <v>0.0539</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5429</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3057</v>
+        <v>0.2172</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0207</v>
+        <v>-0.0355</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2849</v>
+        <v>0.2527</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0134</v>
+        <v>-0.9891</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.509</v>
+        <v>-0.4854</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5044</v>
+        <v>-0.5036</v>
       </c>
       <c r="V6" t="n">
-        <v>0.068</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.068</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9609</v>
+        <v>-1.8863</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.669</v>
+        <v>-2.2579</v>
       </c>
       <c r="F7" t="n">
-        <v>0.708</v>
+        <v>0.3716</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0653</v>
+        <v>-2.0083</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0066</v>
+        <v>1.0145</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.0719</v>
+        <v>-3.0228</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2632</v>
+        <v>-0.0295</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2433</v>
+        <v>1.3394</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.5065</v>
+        <v>-1.3689</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8021</v>
+        <v>-1.9788</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2366</v>
+        <v>-0.3249</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5655</v>
+        <v>-1.6539</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8449</v>
+        <v>0.8161</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1843</v>
+        <v>-0.1458</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0291</v>
+        <v>0.9619</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7794</v>
+        <v>0.8384</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1179</v>
+        <v>-2.141</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4334</v>
+        <v>-1.2221</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6845</v>
+        <v>-0.9189000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.831</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0818</v>
+        <v>-0.1155</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7492</v>
+        <v>-0.7277</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.9791</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2381</v>
+        <v>-0.2129</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0875</v>
+        <v>1.192</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6803</v>
+        <v>-1.8222</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1563</v>
+        <v>0.0974</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8367</v>
+        <v>-1.9197</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3674</v>
+        <v>-1.3231</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2824</v>
+        <v>-1.2275</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0956</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5897</v>
+        <v>-2.5821</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4948</v>
+        <v>-0.3502</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0949</v>
+        <v>-2.2318</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7134</v>
+        <v>-1.7148</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9623</v>
+        <v>-0.9627</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7511</v>
+        <v>-0.7521</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1874</v>
+        <v>0.293</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3763</v>
+        <v>-0.3232</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5637</v>
+        <v>0.6163</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9009</v>
+        <v>-2.0078</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3149</v>
+        <v>-1.3684</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0764</v>
+        <v>-0.062</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5181</v>
+        <v>0.5252</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5944</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.388</v>
+        <v>-4.2619</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.232</v>
+        <v>-3.9088</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.156</v>
+        <v>-0.3531</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9204</v>
+        <v>-1.8924</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1661</v>
+        <v>0.2084</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0866</v>
+        <v>-2.1008</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7688</v>
+        <v>-0.6097</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5453</v>
+        <v>0.6544</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3141</v>
+        <v>-1.264</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1516</v>
+        <v>-1.2828</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3791</v>
+        <v>-0.446</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7725</v>
+        <v>-0.8368</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.401</v>
+        <v>-3.3105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.2015</v>
+        <v>-5.0631</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2938</v>
+        <v>2.2652</v>
       </c>
       <c r="T10" t="n">
-        <v>3.179</v>
+        <v>3.1398</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8852</v>
+        <v>-0.8746</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3604</v>
+        <v>-1.3242</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.4407</v>
+        <v>-1.3758</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0803</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4627</v>
+        <v>-4.4885</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9694</v>
+        <v>-3.7083</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4934</v>
+        <v>-0.7801</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.9844</v>
+        <v>-3.9964</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9253</v>
+        <v>-1.8693</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0591</v>
+        <v>-2.1271</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1688</v>
+        <v>-1.0149</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4887</v>
+        <v>-1.3391</v>
       </c>
       <c r="L11" t="n">
-        <v>0.32</v>
+        <v>0.3242</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.8157</v>
+        <v>-2.9814</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4366</v>
+        <v>-0.5302</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.3791</v>
+        <v>-2.4513</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S11" t="n">
-        <v>1.7941</v>
+        <v>1.7464</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.8897</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9136</v>
+        <v>0.8567</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.872</v>
+        <v>-0.8754</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1918</v>
+        <v>-0.2133</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5096</v>
+        <v>-4.4954</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7031</v>
+        <v>-4.4536</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1935</v>
+        <v>-0.0418</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.308</v>
+        <v>-4.226</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.7989</v>
+        <v>-2.7283</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5091</v>
+        <v>-1.4977</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.2987</v>
+        <v>-4.0854</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.0265</v>
+        <v>-2.8863</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2722</v>
+        <v>-1.1991</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.1406</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2276</v>
+        <v>0.158</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2369</v>
+        <v>-0.2986</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6706</v>
+        <v>-0.6461</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4044</v>
+        <v>-0.3682</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2662</v>
+        <v>-0.2779</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7316</v>
+        <v>-1.7654</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7316</v>
+        <v>-1.7654</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.002</v>
+        <v>-15.9977</v>
       </c>
       <c r="E13" t="n">
-        <v>-17.1316</v>
+        <v>-14.9822</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1294</v>
+        <v>-1.0152</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.423300000000001</v>
+        <v>-9.3687</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.7461</v>
+        <v>-4.6516</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.6772</v>
+        <v>-4.7172</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9068999999999994</v>
+        <v>0.4063000000000008</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.3101</v>
+        <v>-2.5468</v>
       </c>
       <c r="L13" t="n">
-        <v>2.4034</v>
+        <v>2.9534</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.516500000000001</v>
+        <v>-9.774999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4358</v>
+        <v>-2.1047</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.081</v>
+        <v>-7.670500000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.0004</v>
+        <v>-0.9736000000000002</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.0049</v>
+        <v>-16.5524</v>
       </c>
       <c r="R13" t="n">
-        <v>16.0047</v>
+        <v>15.579</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1007</v>
+        <v>1.112</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6021</v>
+        <v>1.8045</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5014000000000001</v>
+        <v>-0.6924000000000003</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.6791</v>
+        <v>-6.7674</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.8219000000000002</v>
+        <v>-0.6404999999999997</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.857200000000001</v>
+        <v>-6.127000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SOCAGE JOVENS L’ELIANA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SOCAGE JOVENS L’ELIANA.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1608</v>
+        <v>2.52</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1019</v>
+        <v>1.6002</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0589</v>
+        <v>0.9198</v>
       </c>
       <c r="G2" t="n">
         <v>1.5553</v>
@@ -610,13 +610,13 @@
         <v>1.5579</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1034</v>
+        <v>-0.7441</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.671</v>
+        <v>-0.1726</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4324</v>
+        <v>-0.5715</v>
       </c>
       <c r="V2" t="n">
         <v>0.3457</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6663</v>
+        <v>1.6593</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4832</v>
+        <v>0.7823</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1831</v>
+        <v>0.877</v>
       </c>
       <c r="G3" t="n">
         <v>5.0899</v>
@@ -688,13 +688,13 @@
         <v>1.9474</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8529</v>
+        <v>-0.8599</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9183</v>
+        <v>-0.6193</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0654</v>
+        <v>-0.2407</v>
       </c>
       <c r="V3" t="n">
         <v>-2.3759</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>M. PAÑOS HUERTAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6172</v>
+        <v>0.6079</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8686</v>
+        <v>0.6079</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2513</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6689</v>
+        <v>0.6079</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6087</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0602</v>
+        <v>0.6079</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4769</v>
+        <v>0.6079</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2469</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.77</v>
+        <v>0.6079</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.192</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3618</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8302</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9737</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9737</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2609</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.066</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1949</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0516</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. PAÑOS HUERTAS</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6079</v>
+        <v>-0.3239</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6079</v>
+        <v>-0.1282</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.1957</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6079</v>
+        <v>-1.6689</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-1.6087</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6079</v>
+        <v>-0.0602</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6079</v>
+        <v>-0.4769</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-1.2469</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6079</v>
+        <v>0.77</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.192</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.3618</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.8302</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.3198</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.0692</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.2506</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.0516</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2279</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BALLESTER FERRANDIS</t>
+          <t>B. MONDRAGON VIDAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1947</v>
+        <v>-0.5553</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1429</v>
+        <v>-0.026</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9482</v>
+        <v>-0.5294</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2718</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0184</v>
+        <v>-0.1155</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2902</v>
+        <v>-0.7277</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.489</v>
+        <v>0.9791</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0539</v>
+        <v>-0.2129</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5429</v>
+        <v>1.192</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2172</v>
+        <v>-1.8222</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0355</v>
+        <v>0.0974</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2527</v>
+        <v>-1.9197</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1684</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1684</v>
+        <v>1.5579</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9891</v>
+        <v>0.2626</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4854</v>
+        <v>-0.0314</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5036</v>
+        <v>0.2939</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. MONTANO LINARES</t>
+          <t>J. BALLESTER FERRANDIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8863</v>
+        <v>-0.9119</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2579</v>
+        <v>-1.9435</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3716</v>
+        <v>1.0317</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0083</v>
+        <v>-0.2718</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0145</v>
+        <v>0.0184</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.0228</v>
+        <v>-0.2902</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0295</v>
+        <v>-0.489</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3394</v>
+        <v>0.0539</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3689</v>
+        <v>-0.5429</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9788</v>
+        <v>0.2172</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3249</v>
+        <v>-0.0355</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6539</v>
+        <v>0.2527</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.921</v>
+        <v>-1.1684</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9474</v>
+        <v>1.1684</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8161</v>
+        <v>-0.7063</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1458</v>
+        <v>-0.2861</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9619</v>
+        <v>-0.4202</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2795</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8384</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. MONDRAGON VIDAL</t>
+          <t>K. MONTANO LINARES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.141</v>
+        <v>-1.861</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2221</v>
+        <v>-1.7595</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.1015</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-2.0083</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1155</v>
+        <v>1.0145</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7277</v>
+        <v>-3.0228</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9791</v>
+        <v>-0.0295</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2129</v>
+        <v>1.3394</v>
       </c>
       <c r="L8" t="n">
-        <v>1.192</v>
+        <v>-1.3689</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8222</v>
+        <v>-1.9788</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0974</v>
+        <v>-0.3249</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9197</v>
+        <v>-1.6539</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5842000000000001</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9737</v>
+        <v>-2.921</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5579</v>
+        <v>1.9474</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3231</v>
+        <v>0.8415</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2275</v>
+        <v>0.3526</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0956</v>
+        <v>0.4889</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0.2795</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.8384</v>
       </c>
       <c r="X8" t="n">
         <v>-0.5590000000000001</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5821</v>
+        <v>-2.6585</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3502</v>
+        <v>-0.6493</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2318</v>
+        <v>-2.0092</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7148</v>
@@ -1156,13 +1156,13 @@
         <v>0.9737</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.062</v>
+        <v>-0.1384</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5252</v>
+        <v>0.2261</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3646</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6105</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. AZNAR MARTINEZ</t>
+          <t>M. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2619</v>
+        <v>-3.7466</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9088</v>
+        <v>-3.9552</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3531</v>
+        <v>0.2086</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8924</v>
+        <v>-4.226</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2084</v>
+        <v>-2.7283</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1008</v>
+        <v>-1.4977</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6097</v>
+        <v>-4.0854</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6544</v>
+        <v>-2.8863</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.264</v>
+        <v>-1.1991</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2828</v>
+        <v>-0.1406</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.446</v>
+        <v>0.158</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8368</v>
+        <v>-0.2986</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.3105</v>
+        <v>2.1421</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.0631</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7526</v>
+        <v>2.1421</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2652</v>
+        <v>0.1027</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1398</v>
+        <v>0.1302</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8746</v>
+        <v>-0.0275</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3242</v>
+        <v>-1.7654</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.3758</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0516</v>
+        <v>-1.7654</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4885</v>
+        <v>-5.0612</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7083</v>
+        <v>-3.808</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7801</v>
+        <v>-1.2531</v>
       </c>
       <c r="G11" t="n">
         <v>-3.9964</v>
@@ -1312,13 +1312,13 @@
         <v>1.5579</v>
       </c>
       <c r="S11" t="n">
-        <v>1.7464</v>
+        <v>1.1737</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8897</v>
+        <v>0.79</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8567</v>
+        <v>0.3837</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8754</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. PANOS HUERTAS</t>
+          <t>A. AZNAR MARTINEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4954</v>
+        <v>-5.6665</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4536</v>
+        <v>-5.7029</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0418</v>
+        <v>0.0364</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.226</v>
+        <v>-1.8924</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.7283</v>
+        <v>0.2084</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4977</v>
+        <v>-2.1008</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.0854</v>
+        <v>-0.6097</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.8863</v>
+        <v>0.6544</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1991</v>
+        <v>-1.264</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1406</v>
+        <v>-1.2828</v>
       </c>
       <c r="N12" t="n">
-        <v>0.158</v>
+        <v>-0.446</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2986</v>
+        <v>-0.8368</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1421</v>
+        <v>-3.3105</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-5.0631</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1421</v>
+        <v>1.7526</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6461</v>
+        <v>0.8606</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3682</v>
+        <v>1.3456</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2779</v>
+        <v>-0.485</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7654</v>
+        <v>-1.3242</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-1.3758</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7654</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="13">
@@ -1429,28 +1429,28 @@
         <v>-14.9822</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0152</v>
+        <v>-1.0154</v>
       </c>
       <c r="G13" t="n">
         <v>-9.3687</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.6516</v>
+        <v>-4.651599999999999</v>
       </c>
       <c r="I13" t="n">
         <v>-4.7172</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4063000000000008</v>
+        <v>0.4063</v>
       </c>
       <c r="K13" t="n">
         <v>-2.5468</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9534</v>
+        <v>2.953399999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.774999999999999</v>
+        <v>-9.775</v>
       </c>
       <c r="N13" t="n">
         <v>-2.1047</v>
@@ -1468,13 +1468,13 @@
         <v>15.579</v>
       </c>
       <c r="S13" t="n">
-        <v>1.112</v>
+        <v>1.1122</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8045</v>
+        <v>1.8043</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6924000000000003</v>
+        <v>-0.6924000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-6.7674</v>
@@ -1483,7 +1483,7 @@
         <v>-0.6404999999999997</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.127000000000001</v>
+        <v>-6.127000000000002</v>
       </c>
     </row>
   </sheetData>
